--- a/dataset/scifact_F40.xlsx
+++ b/dataset/scifact_F40.xlsx
@@ -441,7 +441,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -513,12 +513,6 @@
       <family val="1"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -569,7 +563,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -616,10 +610,6 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1390,7 +1380,7 @@
       <c r="C41" s="1" t="n">
         <v>185</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="5" t="s">
         <v>121</v>
       </c>
     </row>
